--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'E-mail wordings'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Schedules and timings'!$A$12:$K$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Schedules and timings'!$12:$12</definedName>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>21 items</t>
+          <t>23 items</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="F6" s="24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="24">
         <f>COUNTIF('E-mail wordings'!K:K,"Open")</f>
@@ -8845,7 +8845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10333,47 +10333,47 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>RC-EML-21</t>
+          <t>NT-21</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Sender and footer of the e-mails</t>
+          <t>Identity event to review</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>BRD NFR p.17 (10)</t>
+          <t>BRD 1.001 (user enrolment); BRD NFR p.13 (1)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Annex T</t>
+          <t>Annex T; FRUM.002.02, FRUM.003.03</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>The sender address of each environment and, if required, the standard footer or disclaimer of BDOI e-mails.</t>
+          <t>Approve the wording, the trigger and the recipients. Subject: Identity event &lt;event no&gt; needs review. Text: &lt;UIDM-ISC | Enterprise SSO&gt; event &lt;Joiner | Mover | Leaver | Rehire | Status&gt; of Windows ID &lt;Windows ID&gt; was &lt;refused | failed&gt;: &lt;reason&gt;</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>Address per environment; footer text</t>
+          <t>Approve, or the new wording</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>bibs-noreply@ (domain of BDOI)</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Process Owner (Business Administration)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>16-Jul-2027</t>
+          <t>01-Dec-2026</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr"/>
@@ -10383,8 +10383,114 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>NT-22</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Break-glass sign-in</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>BRD NFR p.17 (1)</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Annex T; FRUM.001.06</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: Break-glass sign-in. Text: Break-glass administrator &lt;name&gt; (&lt;user ID&gt;) signed in with a local password at &lt;dd-MMM-yyyy HH:mm&gt; from &lt;address&gt;. Review the use within one working day.</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>Process Owner (Business Administration)</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>01-Dec-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="inlineStr"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>RC-EML-21</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Sender and footer of the e-mails</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>BRD NFR p.17 (10)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Annex T</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>The sender address of each environment and, if required, the standard footer or disclaimer of BDOI e-mails.</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Address per environment; footer text</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>bibs-noreply@ (domain of BDOI)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>BDOI IT</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr"/>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:K34"/>
+  <autoFilter ref="A12:K36"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -10393,7 +10499,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K336" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -12278,7 +12384,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of password history: Previous passwords refused (local accounts). Delivered: 8 (to be set to 10).</t>
+          <t>Confirm the value of password history: Previous passwords refused (local accounts). Delivered: 10.</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -12288,7 +12394,7 @@
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>8 (to be set to 10)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
